--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F95774-62E4-49F2-9DAD-54573BC885F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF346A9E-23D4-419C-8E0C-2B28FE8DB3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>overall better</t>
+  </si>
+  <si>
+    <t>good enough</t>
   </si>
 </sst>
 </file>
@@ -1345,26 +1348,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>40</v>
+      </c>
+      <c r="D13" s="14">
+        <v>210</v>
+      </c>
+      <c r="E13" s="14">
+        <v>135</v>
+      </c>
+      <c r="F13" s="14">
+        <v>240</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>100</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1205</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>235</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF346A9E-23D4-419C-8E0C-2B28FE8DB3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F76374-FC5A-42FA-91FF-A34E818453F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>good enough</t>
+  </si>
+  <si>
+    <t>health issues</t>
   </si>
 </sst>
 </file>
@@ -1394,26 +1397,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="14">
+        <v>465</v>
+      </c>
+      <c r="C14" s="14">
+        <v>35</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>75</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1205</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>235</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F76374-FC5A-42FA-91FF-A34E818453F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42CA71D-10D1-4C75-8575-75EB464CEF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>health issues</t>
+  </si>
+  <si>
+    <t>health problem</t>
   </si>
 </sst>
 </file>
@@ -1443,26 +1446,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>50</v>
+      </c>
+      <c r="D15" s="14">
+        <v>210</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42CA71D-10D1-4C75-8575-75EB464CEF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B84704-F1AA-4BEC-A72A-604F552B8782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>health problem</t>
+  </si>
+  <si>
+    <t>It was a good  day.</t>
   </si>
 </sst>
 </file>
@@ -1492,26 +1495,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>390</v>
+      </c>
+      <c r="C16" s="14">
+        <v>35</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>135</v>
+      </c>
+      <c r="F16" s="14">
+        <v>360</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>75</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B84704-F1AA-4BEC-A72A-604F552B8782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB54BC8C-0B6C-4426-9B1F-C1966A31FD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>It was a good  day.</t>
+  </si>
+  <si>
+    <t>energetic day</t>
   </si>
 </sst>
 </file>
@@ -1541,26 +1544,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>400</v>
+      </c>
+      <c r="C17" s="14">
+        <v>40</v>
+      </c>
+      <c r="D17" s="14">
+        <v>160</v>
+      </c>
+      <c r="E17" s="14">
+        <v>100</v>
+      </c>
+      <c r="F17" s="14">
+        <v>240</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB54BC8C-0B6C-4426-9B1F-C1966A31FD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0C708F-9D50-4654-A715-1F338F164AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>energetic day</t>
+  </si>
+  <si>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -1590,26 +1593,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>450</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>300</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0C708F-9D50-4654-A715-1F338F164AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98353EE1-ACFB-4F46-AC10-4A5642AE9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1639,26 +1639,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>55</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>80</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>120</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>795</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>645</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98353EE1-ACFB-4F46-AC10-4A5642AE9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CE03C6-C770-4D98-A957-6AD785EDD3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1685,26 +1685,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="14">
+        <v>380</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>120</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CE03C6-C770-4D98-A957-6AD785EDD3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A229B0C-7C17-429E-B643-9B2667DDF128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>good day</t>
+  </si>
+  <si>
+    <t>A formal day.</t>
   </si>
 </sst>
 </file>
@@ -1731,26 +1734,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>45</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>315</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A229B0C-7C17-429E-B643-9B2667DDF128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B926C0D-7F8D-4B4A-9D87-F11E98427653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>A formal day.</t>
+  </si>
+  <si>
+    <t>nice day.</t>
   </si>
 </sst>
 </file>
@@ -1780,26 +1783,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>380</v>
+      </c>
+      <c r="C22" s="14">
+        <v>65</v>
+      </c>
+      <c r="D22" s="14">
+        <v>300</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>45</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B926C0D-7F8D-4B4A-9D87-F11E98427653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDE6AFB-A115-4534-BBAA-DFCA72109AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>nice day.</t>
+  </si>
+  <si>
+    <t>productive day.</t>
   </si>
 </sst>
 </file>
@@ -1829,26 +1832,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>400</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>360</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>420</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>40</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDE6AFB-A115-4534-BBAA-DFCA72109AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8811776-9860-40A0-AEC3-B32D83F4F8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>productive day.</t>
+  </si>
+  <si>
+    <t>positive day.</t>
   </si>
 </sst>
 </file>
@@ -1878,26 +1881,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>380</v>
+      </c>
+      <c r="C24" s="14">
+        <v>120</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>150</v>
+      </c>
+      <c r="F24" s="14">
+        <v>420</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8811776-9860-40A0-AEC3-B32D83F4F8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54830A1A-F18D-46DF-8522-5BF316BFE9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>positive day.</t>
+  </si>
+  <si>
+    <t>normal day.</t>
   </si>
 </sst>
 </file>
@@ -1927,26 +1930,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>380</v>
+      </c>
+      <c r="E25" s="14">
+        <v>190</v>
+      </c>
+      <c r="F25" s="14">
+        <v>60</v>
+      </c>
+      <c r="G25" s="14">
+        <v>1</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54830A1A-F18D-46DF-8522-5BF316BFE9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C89EA-F274-425D-B83F-C042096700A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1976,26 +1976,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="14">
+        <v>300</v>
+      </c>
+      <c r="C26" s="14">
+        <v>120</v>
+      </c>
+      <c r="D26" s="14">
+        <v>420</v>
+      </c>
+      <c r="E26" s="14">
+        <v>180</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C89EA-F274-425D-B83F-C042096700A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D6508D-8555-453B-9F7B-74282F5C3741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>normal day.</t>
+  </si>
+  <si>
+    <t>average day.</t>
   </si>
 </sst>
 </file>
@@ -2022,26 +2025,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>320</v>
+      </c>
+      <c r="C27" s="14">
+        <v>80</v>
+      </c>
+      <c r="D27" s="14">
+        <v>360</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14">
+        <v>360</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D6508D-8555-453B-9F7B-74282F5C3741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279480C9-237A-437D-92C8-23C4D69CF236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>average day.</t>
+  </si>
+  <si>
+    <t>fun day.</t>
   </si>
 </sst>
 </file>
@@ -2071,26 +2074,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="14">
+        <v>380</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>300</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279480C9-237A-437D-92C8-23C4D69CF236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05218F24-001D-4C97-8248-1B00FABC2187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>fun day.</t>
+  </si>
+  <si>
+    <t>peaceful day.</t>
   </si>
 </sst>
 </file>
@@ -2120,26 +2123,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05218F24-001D-4C97-8248-1B00FABC2187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F27FFC-E53A-4F6A-B3E4-CDE40B6C0169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>peaceful day.</t>
+  </si>
+  <si>
+    <t>Thoughtful day.</t>
   </si>
 </sst>
 </file>
@@ -2169,26 +2172,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>400</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>60</v>
+      </c>
+      <c r="E30" s="14">
+        <v>180</v>
+      </c>
+      <c r="F30" s="14">
+        <v>120</v>
+      </c>
+      <c r="G30" s="14">
+        <v>2</v>
+      </c>
+      <c r="H30" s="14">
+        <v>100</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F27FFC-E53A-4F6A-B3E4-CDE40B6C0169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DB450A-A107-43CA-A321-4996F06FD0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Thoughtful day.</t>
+  </si>
+  <si>
+    <t>pretty good.</t>
   </si>
 </sst>
 </file>
@@ -2218,26 +2221,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>380</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>420</v>
+      </c>
+      <c r="G31" s="14">
+        <v>7</v>
+      </c>
+      <c r="H31" s="14">
+        <v>60</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DB450A-A107-43CA-A321-4996F06FD0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6ADA16-A72E-4BC9-B56E-4DDCBB576DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>pretty good.</t>
+  </si>
+  <si>
+    <t>superb day.</t>
   </si>
 </sst>
 </file>
@@ -2267,29 +2270,53 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>350</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>450</v>
+      </c>
+      <c r="E32" s="14">
+        <v>300</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>40</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
+      <c r="A33" s="8"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
